--- a/artfynd/A 58783-2025 artfynd.xlsx
+++ b/artfynd/A 58783-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,6 +930,112 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129930241</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97661</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nävekvarn, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>601619</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6503656</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58783-2025 artfynd.xlsx
+++ b/artfynd/A 58783-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>129930241</v>
       </c>
       <c r="B4" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58783-2025 artfynd.xlsx
+++ b/artfynd/A 58783-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>129930241</v>
       </c>
       <c r="B4" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58783-2025 artfynd.xlsx
+++ b/artfynd/A 58783-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>129930241</v>
       </c>
       <c r="B4" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58783-2025 artfynd.xlsx
+++ b/artfynd/A 58783-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>129930241</v>
       </c>
       <c r="B4" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58783-2025 artfynd.xlsx
+++ b/artfynd/A 58783-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>129930241</v>
       </c>
       <c r="B4" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58783-2025 artfynd.xlsx
+++ b/artfynd/A 58783-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>129930241</v>
       </c>
       <c r="B4" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58783-2025 artfynd.xlsx
+++ b/artfynd/A 58783-2025 artfynd.xlsx
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92834595</v>
+        <v>94203495</v>
       </c>
       <c r="B2" t="n">
-        <v>57193</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206004</v>
+        <v>102118</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,11 +708,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2K+</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601539.6988696788</v>
+        <v>601540</v>
       </c>
       <c r="R2" t="n">
-        <v>6503674.285001103</v>
+        <v>6503674</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -757,27 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:14</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sprang över vägen.</t>
+          <t>23:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,39 +791,34 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Gustafsson, Jan Karlsson</t>
+          <t>Jan Karlsson, Jan Gustafsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109841394</v>
+        <v>92834595</v>
       </c>
       <c r="B3" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102118</v>
+        <v>206004</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -842,15 +831,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2K+</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -890,22 +875,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sprang över vägen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,7 +925,7 @@
         <v>129930241</v>
       </c>
       <c r="B4" t="n">
-        <v>97791</v>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58783-2025 artfynd.xlsx
+++ b/artfynd/A 58783-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94203495</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92834595</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,8 +1040,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129930241</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>